--- a/data/secciones.xlsx
+++ b/data/secciones.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="9144" windowHeight="5375"/>
+    <workbookView windowWidth="11315" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -41,43 +41,43 @@
     <t>Chocolate</t>
   </si>
   <si>
-    <t>https://pngimg.com/uploads/chocolate/chocolate_PNG27.png</t>
+    <t>https://github.com/Elian-digital/Candy-Shop-Analytics-Dashboard/blob/main/images/icons/chocolate.png?raw=true</t>
   </si>
   <si>
     <t>Caramel</t>
   </si>
   <si>
-    <t>https://static.vecteezy.com/system/resources/previews/048/235/567/non_2x/three-sweet-caramel-candy-cubes-on-transparent-background-free-png.png</t>
+    <t>https://github.com/Elian-digital/Candy-Shop-Analytics-Dashboard/blob/main/images/icons/Caramel.png?raw=true</t>
   </si>
   <si>
     <t>gum</t>
   </si>
   <si>
-    <t>https://static.vecteezy.com/system/resources/previews/027/992/680/non_2x/pads-of-bubble-gum-mint-chewing-gum-3d-illustration-png.png</t>
+    <t>https://github.com/Elian-digital/Candy-Shop-Analytics-Dashboard/blob/main/images/icons/gum.png?raw=true</t>
   </si>
   <si>
     <t>Hard candy</t>
   </si>
   <si>
-    <t>https://static.vecteezy.com/system/resources/thumbnails/047/830/150/small_2x/colorful-wrapped-candy-with-red-green-and-white-stripes-perfect-for-holiday-themes-christmas-designs-or-festive-decorations-png.png</t>
+    <t>https://github.com/Elian-digital/Candy-Shop-Analytics-Dashboard/blob/main/images/icons/hardCandy.png?raw=true</t>
   </si>
   <si>
     <t>gummy</t>
   </si>
   <si>
-    <t>https://cdn.pixabay.com/photo/2021/01/15/04/46/gummy-bear-5918425_1280.png</t>
+    <t>https://github.com/Elian-digital/Candy-Shop-Analytics-Dashboard/blob/main/images/icons/osos.png?raw=true</t>
   </si>
   <si>
     <t>chew</t>
   </si>
   <si>
-    <t>https://wallpapers.com/images/hd/chewy-candy-delicacies-png-31-fuqtwiak7wzf4tr7.png</t>
+    <t>https://github.com/Elian-digital/Candy-Shop-Analytics-Dashboard/blob/main/images/icons/chews.png?raw=true</t>
   </si>
   <si>
     <t>chews</t>
   </si>
   <si>
-    <t>https://png.pngtree.com/png-vector/20241012/ourmid/pngtree-chewy-caramel-candy-wrapped-png-image_14042118.png</t>
+    <t>https://github.com/Elian-digital/Candy-Shop-Analytics-Dashboard/blob/main/images/icons/chew.png?raw=true</t>
   </si>
 </sst>
 </file>
@@ -90,7 +90,7 @@
     <numFmt numFmtId="176" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* \-??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,24 +101,17 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -553,28 +546,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -583,125 +579,122 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -761,6 +754,52 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1037590</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1" descr="chew.png"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1743075" y="1066800"/>
+          <a:ext cx="243840" cy="243840"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1059,7 +1098,7 @@
       <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1070,7 +1109,7 @@
       <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1081,7 +1120,7 @@
       <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1092,7 +1131,7 @@
       <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1103,7 +1142,7 @@
       <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1120,15 +1159,10 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="https://pngimg.com/uploads/chocolate/chocolate_PNG27.png"/>
-    <hyperlink ref="C3" r:id="rId2" display="https://static.vecteezy.com/system/resources/previews/048/235/567/non_2x/three-sweet-caramel-candy-cubes-on-transparent-background-free-png.png" tooltip="https://static.vecteezy.com/system/resources/previews/048/235/567/non_2x/three-sweet-caramel-candy-cubes-on-transparent-background-free-png.png"/>
-    <hyperlink ref="C4" r:id="rId3" display="https://static.vecteezy.com/system/resources/previews/027/992/680/non_2x/pads-of-bubble-gum-mint-chewing-gum-3d-illustration-png.png" tooltip="https://static.vecteezy.com/system/resources/previews/027/992/680/non_2x/pads-of-bubble-gum-mint-chewing-gum-3d-illustration-png.png"/>
-    <hyperlink ref="C6" r:id="rId4" display="https://cdn.pixabay.com/photo/2021/01/15/04/46/gummy-bear-5918425_1280.png" tooltip="https://cdn.pixabay.com/photo/2021/01/15/04/46/gummy-bear-5918425_1280.png"/>
-    <hyperlink ref="C7" r:id="rId5" display="https://wallpapers.com/images/hd/chewy-candy-delicacies-png-31-fuqtwiak7wzf4tr7.png" tooltip="https://wallpapers.com/images/hd/chewy-candy-delicacies-png-31-fuqtwiak7wzf4tr7.png"/>
-    <hyperlink ref="C8" r:id="rId6" display="https://png.pngtree.com/png-vector/20241012/ourmid/pngtree-chewy-caramel-candy-wrapped-png-image_14042118.png" tooltip="https://png.pngtree.com/png-vector/20241012/ourmid/pngtree-chewy-caramel-candy-wrapped-png-image_14042118.png"/>
-    <hyperlink ref="C5" r:id="rId7" display="https://static.vecteezy.com/system/resources/thumbnails/047/830/150/small_2x/colorful-wrapped-candy-with-red-green-and-white-stripes-perfect-for-holiday-themes-christmas-designs-or-festive-decorations-png.png" tooltip="https://static.vecteezy.com/system/resources/thumbnails/047/830/150/small_2x/colorful-wrapped-candy-with-red-green-and-white-stripes-perfect-for-holiday-themes-christmas-designs-or-festive-decorations-png.png"/>
+    <hyperlink ref="C8" r:id="rId2" display="https://github.com/Elian-digital/Candy-Shop-Analytics-Dashboard/blob/main/images/icons/chew.png?raw=true"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>